--- a/data_group/emmeans_intervalos_evapo.xlsx
+++ b/data_group/emmeans_intervalos_evapo.xlsx
@@ -41,7 +41,7 @@
     <t xml:space="preserve">PF</t>
   </si>
   <si>
-    <t xml:space="preserve">EVAPO</t>
+    <t xml:space="preserve">PREC</t>
   </si>
   <si>
     <t xml:space="preserve">1-10</t>
@@ -449,16 +449,16 @@
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>1330.86347364189</v>
+        <v>1330.92125830967</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>1314.93065022164</v>
+        <v>1325.33400742935</v>
       </c>
       <c r="G2" t="n">
-        <v>1346.79629706214</v>
+        <v>1336.50850918998</v>
       </c>
     </row>
     <row r="3">
@@ -472,16 +472,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>1382.12156548722</v>
+        <v>1382.15201500733</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="n">
-        <v>1366.18874206697</v>
+        <v>1376.18285297421</v>
       </c>
       <c r="G3" t="n">
-        <v>1398.05438890748</v>
+        <v>1388.12117704045</v>
       </c>
     </row>
     <row r="4">
@@ -495,16 +495,16 @@
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>1412.05663662232</v>
+        <v>1411.97565484059</v>
       </c>
       <c r="E4" t="s">
         <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>1396.12381320208</v>
+        <v>1405.10366521649</v>
       </c>
       <c r="G4" t="n">
-        <v>1427.98946004257</v>
+        <v>1418.84764446469</v>
       </c>
     </row>
     <row r="5">
@@ -518,16 +518,16 @@
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>1431.84486832309</v>
+        <v>1431.67949352573</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
       </c>
       <c r="F5" t="n">
-        <v>1415.91204490285</v>
+        <v>1424.04604300542</v>
       </c>
       <c r="G5" t="n">
-        <v>1447.77769174334</v>
+        <v>1439.31294404605</v>
       </c>
     </row>
     <row r="6">
@@ -541,16 +541,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>1443.26404888539</v>
+        <v>1442.9584936799</v>
       </c>
       <c r="E6" t="s">
         <v>14</v>
       </c>
       <c r="F6" t="n">
-        <v>1427.33122546513</v>
+        <v>1435.44374501589</v>
       </c>
       <c r="G6" t="n">
-        <v>1459.19687230565</v>
+        <v>1450.47324234391</v>
       </c>
     </row>
     <row r="7">
@@ -564,16 +564,16 @@
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>1452.16161460451</v>
+        <v>1451.71859068418</v>
       </c>
       <c r="E7" t="s">
         <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>1436.22879118423</v>
+        <v>1443.94978665891</v>
       </c>
       <c r="G7" t="n">
-        <v>1468.09443802478</v>
+        <v>1459.48739470944</v>
       </c>
     </row>
     <row r="8">
@@ -587,16 +587,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>1457.6497659279</v>
+        <v>1457.27148591561</v>
       </c>
       <c r="E8" t="s">
         <v>16</v>
       </c>
       <c r="F8" t="n">
-        <v>1441.71694250764</v>
+        <v>1448.70935715375</v>
       </c>
       <c r="G8" t="n">
-        <v>1473.58258934815</v>
+        <v>1465.83361467747</v>
       </c>
     </row>
     <row r="9">
@@ -610,16 +610,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>1462.45372068225</v>
+        <v>1462.14138434928</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
       </c>
       <c r="F9" t="n">
-        <v>1446.52089726199</v>
+        <v>1452.75811668675</v>
       </c>
       <c r="G9" t="n">
-        <v>1478.38654410251</v>
+        <v>1471.52465201181</v>
       </c>
     </row>
     <row r="10">
@@ -633,16 +633,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>1465.73652141613</v>
+        <v>1465.48843839538</v>
       </c>
       <c r="E10" t="s">
         <v>18</v>
       </c>
       <c r="F10" t="n">
-        <v>1449.80369799587</v>
+        <v>1455.59356174952</v>
       </c>
       <c r="G10" t="n">
-        <v>1481.66934483639</v>
+        <v>1475.38331504124</v>
       </c>
     </row>
     <row r="11">
@@ -656,16 +656,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>1483.92777644784</v>
+        <v>1484.13207855004</v>
       </c>
       <c r="E11" t="s">
         <v>19</v>
       </c>
       <c r="F11" t="n">
-        <v>1467.9949530276</v>
+        <v>1474.27902040101</v>
       </c>
       <c r="G11" t="n">
-        <v>1499.86059986808</v>
+        <v>1493.98513669906</v>
       </c>
     </row>
     <row r="12">
@@ -679,16 +679,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>1432.90623716409</v>
+        <v>1433.88749308352</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>1416.97341374371</v>
+        <v>1426.95043658478</v>
       </c>
       <c r="G12" t="n">
-        <v>1448.83906058446</v>
+        <v>1440.82454958227</v>
       </c>
     </row>
     <row r="13">
@@ -702,16 +702,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>1455.00689773104</v>
+        <v>1455.98743339993</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>1439.07407431066</v>
+        <v>1449.31292017072</v>
       </c>
       <c r="G13" t="n">
-        <v>1470.93972115142</v>
+        <v>1462.66194662915</v>
       </c>
     </row>
     <row r="14">
@@ -725,16 +725,16 @@
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>1463.29743127562</v>
+        <v>1463.44512333426</v>
       </c>
       <c r="E14" t="s">
         <v>12</v>
       </c>
       <c r="F14" t="n">
-        <v>1447.36460785524</v>
+        <v>1457.00194763022</v>
       </c>
       <c r="G14" t="n">
-        <v>1479.230254696</v>
+        <v>1469.88829903829</v>
       </c>
     </row>
     <row r="15">
@@ -748,16 +748,16 @@
         <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>1478.4414711998</v>
+        <v>1477.97668712092</v>
       </c>
       <c r="E15" t="s">
         <v>13</v>
       </c>
       <c r="F15" t="n">
-        <v>1462.50864777942</v>
+        <v>1470.89802369743</v>
       </c>
       <c r="G15" t="n">
-        <v>1494.37429462019</v>
+        <v>1485.05535054441</v>
       </c>
     </row>
     <row r="16">
@@ -771,16 +771,16 @@
         <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>1485.06395595493</v>
+        <v>1484.43283847898</v>
       </c>
       <c r="E16" t="s">
         <v>14</v>
       </c>
       <c r="F16" t="n">
-        <v>1469.13113253455</v>
+        <v>1475.94396620778</v>
       </c>
       <c r="G16" t="n">
-        <v>1500.99677937531</v>
+        <v>1492.92171075019</v>
       </c>
     </row>
     <row r="17">
@@ -794,16 +794,16 @@
         <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>1489.84467254958</v>
+        <v>1487.80251326846</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
       </c>
       <c r="F17" t="n">
-        <v>1473.9118491292</v>
+        <v>1478.22726899451</v>
       </c>
       <c r="G17" t="n">
-        <v>1505.77749596997</v>
+        <v>1497.37775754242</v>
       </c>
     </row>
     <row r="18">
@@ -817,16 +817,16 @@
         <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>1500.14301950909</v>
+        <v>1494.31946242023</v>
       </c>
       <c r="E18" t="s">
         <v>16</v>
       </c>
       <c r="F18" t="n">
-        <v>1484.21019608872</v>
+        <v>1475.79848511976</v>
       </c>
       <c r="G18" t="n">
-        <v>1516.07584292947</v>
+        <v>1512.84043972071</v>
       </c>
     </row>
     <row r="19">
@@ -840,16 +840,16 @@
         <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>1495.34185817282</v>
+        <v>1508.80661214134</v>
       </c>
       <c r="E19" t="s">
         <v>17</v>
       </c>
       <c r="F19" t="n">
-        <v>1479.40903475244</v>
+        <v>1487.22260867673</v>
       </c>
       <c r="G19" t="n">
-        <v>1511.2746815932</v>
+        <v>1530.39061560596</v>
       </c>
     </row>
     <row r="20">
@@ -863,16 +863,16 @@
         <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>1504.4534083986</v>
+        <v>1510.17370876961</v>
       </c>
       <c r="E20" t="s">
         <v>18</v>
       </c>
       <c r="F20" t="n">
-        <v>1488.22374959201</v>
+        <v>1485.00125440396</v>
       </c>
       <c r="G20" t="n">
-        <v>1520.68306720518</v>
+        <v>1535.34616313526</v>
       </c>
     </row>
     <row r="21">
@@ -886,16 +886,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="n">
-        <v>1520.489505753</v>
+        <v>1514.44684157588</v>
       </c>
       <c r="E21" t="s">
         <v>19</v>
       </c>
       <c r="F21" t="n">
-        <v>1503.44909685684</v>
+        <v>1495.84960941412</v>
       </c>
       <c r="G21" t="n">
-        <v>1537.52991464917</v>
+        <v>1533.04407373765</v>
       </c>
     </row>
     <row r="22">
@@ -909,16 +909,16 @@
         <v>9</v>
       </c>
       <c r="D22" t="n">
-        <v>1432.14349823678</v>
+        <v>1432.90966834147</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
       </c>
       <c r="F22" t="n">
-        <v>1416.21067481639</v>
+        <v>1428.1886788226</v>
       </c>
       <c r="G22" t="n">
-        <v>1448.07632165717</v>
+        <v>1437.63065786033</v>
       </c>
     </row>
     <row r="23">
@@ -932,16 +932,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>1450.55796620607</v>
+        <v>1450.20361612525</v>
       </c>
       <c r="E23" t="s">
         <v>11</v>
       </c>
       <c r="F23" t="n">
-        <v>1434.62514278568</v>
+        <v>1446.13642016173</v>
       </c>
       <c r="G23" t="n">
-        <v>1466.49078962646</v>
+        <v>1454.27081208877</v>
       </c>
     </row>
     <row r="24">
@@ -955,16 +955,16 @@
         <v>9</v>
       </c>
       <c r="D24" t="n">
-        <v>1462.47167837983</v>
+        <v>1462.42895749146</v>
       </c>
       <c r="E24" t="s">
         <v>12</v>
       </c>
       <c r="F24" t="n">
-        <v>1446.53885495944</v>
+        <v>1458.4753661084</v>
       </c>
       <c r="G24" t="n">
-        <v>1478.40450180022</v>
+        <v>1466.38254887451</v>
       </c>
     </row>
     <row r="25">
@@ -978,16 +978,16 @@
         <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>1474.60979956435</v>
+        <v>1473.64127505538</v>
       </c>
       <c r="E25" t="s">
         <v>13</v>
       </c>
       <c r="F25" t="n">
-        <v>1458.67697614395</v>
+        <v>1470.84460981218</v>
       </c>
       <c r="G25" t="n">
-        <v>1490.54262298474</v>
+        <v>1476.43794029859</v>
       </c>
     </row>
     <row r="26">
@@ -1001,16 +1001,16 @@
         <v>9</v>
       </c>
       <c r="D26" t="n">
-        <v>1487.05427128221</v>
+        <v>1485.04013728481</v>
       </c>
       <c r="E26" t="s">
         <v>14</v>
       </c>
       <c r="F26" t="n">
-        <v>1471.12144786182</v>
+        <v>1481.78041076256</v>
       </c>
       <c r="G26" t="n">
-        <v>1502.9870947026</v>
+        <v>1488.29986380707</v>
       </c>
     </row>
     <row r="27">
@@ -1024,16 +1024,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>1486.8523229247</v>
+        <v>1486.84069400848</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
       </c>
       <c r="F27" t="n">
-        <v>1470.9194995043</v>
+        <v>1484.08309021942</v>
       </c>
       <c r="G27" t="n">
-        <v>1502.78514634509</v>
+        <v>1489.59829779754</v>
       </c>
     </row>
     <row r="28">
@@ -1047,16 +1047,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>1484.99353697555</v>
+        <v>1483.0613874103</v>
       </c>
       <c r="E28" t="s">
         <v>16</v>
       </c>
       <c r="F28" t="n">
-        <v>1469.06071355516</v>
+        <v>1477.16682645543</v>
       </c>
       <c r="G28" t="n">
-        <v>1500.92636039593</v>
+        <v>1488.95594836517</v>
       </c>
     </row>
     <row r="29">
@@ -1070,16 +1070,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="n">
-        <v>1508.82716151622</v>
+        <v>1499.9636275987</v>
       </c>
       <c r="E29" t="s">
         <v>17</v>
       </c>
       <c r="F29" t="n">
-        <v>1492.89433809583</v>
+        <v>1490.68581758817</v>
       </c>
       <c r="G29" t="n">
-        <v>1524.75998493661</v>
+        <v>1509.24143760923</v>
       </c>
     </row>
     <row r="30">
@@ -1093,16 +1093,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="n">
-        <v>1494.51564360811</v>
+        <v>1493.14335311069</v>
       </c>
       <c r="E30" t="s">
         <v>18</v>
       </c>
       <c r="F30" t="n">
-        <v>1478.58282018771</v>
+        <v>1484.28778572357</v>
       </c>
       <c r="G30" t="n">
-        <v>1510.4484670285</v>
+        <v>1501.99892049781</v>
       </c>
     </row>
     <row r="31">
@@ -1116,16 +1116,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="n">
-        <v>1491.16754639554</v>
+        <v>1483.25512630339</v>
       </c>
       <c r="E31" t="s">
         <v>19</v>
       </c>
       <c r="F31" t="n">
-        <v>1475.23472297515</v>
+        <v>1473.8640915453</v>
       </c>
       <c r="G31" t="n">
-        <v>1507.10036981594</v>
+        <v>1492.64616106148</v>
       </c>
     </row>
     <row r="32">
@@ -1139,16 +1139,16 @@
         <v>9</v>
       </c>
       <c r="D32" t="n">
-        <v>1426.68766412214</v>
+        <v>1426.64011291527</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
       </c>
       <c r="F32" t="n">
-        <v>1409.37160729215</v>
+        <v>1424.61069711753</v>
       </c>
       <c r="G32" t="n">
-        <v>1444.00372095213</v>
+        <v>1428.669528713</v>
       </c>
     </row>
     <row r="33">
@@ -1162,16 +1162,16 @@
         <v>9</v>
       </c>
       <c r="D33" t="n">
-        <v>1444.25220824753</v>
+        <v>1443.94470306627</v>
       </c>
       <c r="E33" t="s">
         <v>11</v>
       </c>
       <c r="F33" t="n">
-        <v>1426.93615141754</v>
+        <v>1441.85535042294</v>
       </c>
       <c r="G33" t="n">
-        <v>1461.56826507752</v>
+        <v>1446.0340557096</v>
       </c>
     </row>
     <row r="34">
@@ -1185,16 +1185,16 @@
         <v>9</v>
       </c>
       <c r="D34" t="n">
-        <v>1459.97646615278</v>
+        <v>1458.52646014076</v>
       </c>
       <c r="E34" t="s">
         <v>12</v>
       </c>
       <c r="F34" t="n">
-        <v>1442.66040932279</v>
+        <v>1456.29057228837</v>
       </c>
       <c r="G34" t="n">
-        <v>1477.29252298277</v>
+        <v>1460.76234799315</v>
       </c>
     </row>
     <row r="35">
@@ -1208,16 +1208,16 @@
         <v>9</v>
       </c>
       <c r="D35" t="n">
-        <v>1470.74166834557</v>
+        <v>1469.97061702399</v>
       </c>
       <c r="E35" t="s">
         <v>13</v>
       </c>
       <c r="F35" t="n">
-        <v>1453.42561151558</v>
+        <v>1468.15440146208</v>
       </c>
       <c r="G35" t="n">
-        <v>1488.05772517556</v>
+        <v>1471.7868325859</v>
       </c>
     </row>
     <row r="36">
@@ -1231,16 +1231,16 @@
         <v>9</v>
       </c>
       <c r="D36" t="n">
-        <v>1477.17485663625</v>
+        <v>1477.06704247381</v>
       </c>
       <c r="E36" t="s">
         <v>14</v>
       </c>
       <c r="F36" t="n">
-        <v>1459.85879980626</v>
+        <v>1475.83273438611</v>
       </c>
       <c r="G36" t="n">
-        <v>1494.49091346624</v>
+        <v>1478.30135056152</v>
       </c>
     </row>
     <row r="37">
@@ -1254,16 +1254,16 @@
         <v>9</v>
       </c>
       <c r="D37" t="n">
-        <v>1487.99776698785</v>
+        <v>1487.45490797229</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
       </c>
       <c r="F37" t="n">
-        <v>1470.68171015786</v>
+        <v>1485.83693461535</v>
       </c>
       <c r="G37" t="n">
-        <v>1505.31382381784</v>
+        <v>1489.07288132924</v>
       </c>
     </row>
     <row r="38">
@@ -1277,16 +1277,16 @@
         <v>9</v>
       </c>
       <c r="D38" t="n">
-        <v>1494.61392367236</v>
+        <v>1492.54010989591</v>
       </c>
       <c r="E38" t="s">
         <v>16</v>
       </c>
       <c r="F38" t="n">
-        <v>1477.29786684237</v>
+        <v>1487.92815579407</v>
       </c>
       <c r="G38" t="n">
-        <v>1511.92998050235</v>
+        <v>1497.15206399774</v>
       </c>
     </row>
     <row r="39">
@@ -1300,16 +1300,16 @@
         <v>9</v>
       </c>
       <c r="D39" t="n">
-        <v>1494.65099524967</v>
+        <v>1493.43885671061</v>
       </c>
       <c r="E39" t="s">
         <v>17</v>
       </c>
       <c r="F39" t="n">
-        <v>1477.33493841968</v>
+        <v>1487.29763264938</v>
       </c>
       <c r="G39" t="n">
-        <v>1511.96705207966</v>
+        <v>1499.58008077183</v>
       </c>
     </row>
     <row r="40">
@@ -1323,16 +1323,16 @@
         <v>9</v>
       </c>
       <c r="D40" t="n">
-        <v>1497.19375049926</v>
+        <v>1500.79233048946</v>
       </c>
       <c r="E40" t="s">
         <v>18</v>
       </c>
       <c r="F40" t="n">
-        <v>1479.87769366927</v>
+        <v>1492.23490192869</v>
       </c>
       <c r="G40" t="n">
-        <v>1514.50980732925</v>
+        <v>1509.34975905023</v>
       </c>
     </row>
     <row r="41">
@@ -1346,16 +1346,16 @@
         <v>9</v>
       </c>
       <c r="D41" t="n">
-        <v>1467.77195883381</v>
+        <v>1470.88517574168</v>
       </c>
       <c r="E41" t="s">
         <v>19</v>
       </c>
       <c r="F41" t="n">
-        <v>1450.45590200382</v>
+        <v>1464.34152215544</v>
       </c>
       <c r="G41" t="n">
-        <v>1485.0880156638</v>
+        <v>1477.42882932792</v>
       </c>
     </row>
     <row r="42">
@@ -1369,16 +1369,16 @@
         <v>9</v>
       </c>
       <c r="D42" t="n">
-        <v>1451.68234763814</v>
+        <v>1451.62869544753</v>
       </c>
       <c r="E42" t="s">
         <v>10</v>
       </c>
       <c r="F42" t="n">
-        <v>1437.18266205133</v>
+        <v>1442.98790873623</v>
       </c>
       <c r="G42" t="n">
-        <v>1466.18203322494</v>
+        <v>1460.26948215883</v>
       </c>
     </row>
     <row r="43">
@@ -1392,16 +1392,16 @@
         <v>9</v>
       </c>
       <c r="D43" t="n">
-        <v>1485.45569455212</v>
+        <v>1485.44674878223</v>
       </c>
       <c r="E43" t="s">
         <v>11</v>
       </c>
       <c r="F43" t="n">
-        <v>1470.95600896531</v>
+        <v>1476.67596912036</v>
       </c>
       <c r="G43" t="n">
-        <v>1499.95538013893</v>
+        <v>1494.2175284441</v>
       </c>
     </row>
     <row r="44">
@@ -1415,16 +1415,16 @@
         <v>9</v>
       </c>
       <c r="D44" t="n">
-        <v>1507.08286170828</v>
+        <v>1507.06170211027</v>
       </c>
       <c r="E44" t="s">
         <v>12</v>
       </c>
       <c r="F44" t="n">
-        <v>1492.58317612146</v>
+        <v>1498.73593315741</v>
       </c>
       <c r="G44" t="n">
-        <v>1521.5825472951</v>
+        <v>1515.38747106312</v>
       </c>
     </row>
     <row r="45">
@@ -1438,16 +1438,16 @@
         <v>9</v>
       </c>
       <c r="D45" t="n">
-        <v>1520.86023487293</v>
+        <v>1520.84180632873</v>
       </c>
       <c r="E45" t="s">
         <v>13</v>
       </c>
       <c r="F45" t="n">
-        <v>1506.36054928611</v>
+        <v>1513.73261661949</v>
       </c>
       <c r="G45" t="n">
-        <v>1535.35992045975</v>
+        <v>1527.95099603796</v>
       </c>
     </row>
     <row r="46">
@@ -1461,16 +1461,16 @@
         <v>9</v>
       </c>
       <c r="D46" t="n">
-        <v>1522.90642865901</v>
+        <v>1522.85464053761</v>
       </c>
       <c r="E46" t="s">
         <v>14</v>
       </c>
       <c r="F46" t="n">
-        <v>1508.4067430722</v>
+        <v>1516.51517122329</v>
       </c>
       <c r="G46" t="n">
-        <v>1537.40611424582</v>
+        <v>1529.19410985193</v>
       </c>
     </row>
     <row r="47">
@@ -1484,16 +1484,16 @@
         <v>9</v>
       </c>
       <c r="D47" t="n">
-        <v>1518.41350583547</v>
+        <v>1518.53814340554</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
       </c>
       <c r="F47" t="n">
-        <v>1503.91382024865</v>
+        <v>1511.00531971339</v>
       </c>
       <c r="G47" t="n">
-        <v>1532.91319142229</v>
+        <v>1526.0709670977</v>
       </c>
     </row>
     <row r="48">
@@ -1507,16 +1507,16 @@
         <v>9</v>
       </c>
       <c r="D48" t="n">
-        <v>1523.00537729827</v>
+        <v>1523.32064008095</v>
       </c>
       <c r="E48" t="s">
         <v>16</v>
       </c>
       <c r="F48" t="n">
-        <v>1508.50569171145</v>
+        <v>1513.98463754783</v>
       </c>
       <c r="G48" t="n">
-        <v>1537.50506288508</v>
+        <v>1532.65664261406</v>
       </c>
     </row>
     <row r="49">
@@ -1530,16 +1530,16 @@
         <v>9</v>
       </c>
       <c r="D49" t="n">
-        <v>1525.45265747429</v>
+        <v>1525.97618077119</v>
       </c>
       <c r="E49" t="s">
         <v>17</v>
       </c>
       <c r="F49" t="n">
-        <v>1510.95297188747</v>
+        <v>1515.21622641144</v>
       </c>
       <c r="G49" t="n">
-        <v>1539.95234306111</v>
+        <v>1536.73613513094</v>
       </c>
     </row>
     <row r="50">
@@ -1553,16 +1553,16 @@
         <v>9</v>
       </c>
       <c r="D50" t="n">
-        <v>1526.51902110975</v>
+        <v>1527.18180104607</v>
       </c>
       <c r="E50" t="s">
         <v>18</v>
       </c>
       <c r="F50" t="n">
-        <v>1512.01933552292</v>
+        <v>1515.13383136639</v>
       </c>
       <c r="G50" t="n">
-        <v>1541.01870669658</v>
+        <v>1539.22977072575</v>
       </c>
     </row>
     <row r="51">
@@ -1576,16 +1576,16 @@
         <v>9</v>
       </c>
       <c r="D51" t="n">
-        <v>1529.44628125805</v>
+        <v>1530.17365064927</v>
       </c>
       <c r="E51" t="s">
         <v>19</v>
       </c>
       <c r="F51" t="n">
-        <v>1514.94659567124</v>
+        <v>1515.66493922548</v>
       </c>
       <c r="G51" t="n">
-        <v>1543.94596684485</v>
+        <v>1544.68236207305</v>
       </c>
     </row>
     <row r="52">
@@ -1599,16 +1599,16 @@
         <v>9</v>
       </c>
       <c r="D52" t="n">
-        <v>1465.97121846272</v>
+        <v>1466.39909072731</v>
       </c>
       <c r="E52" t="s">
         <v>10</v>
       </c>
       <c r="F52" t="n">
-        <v>1451.47153287589</v>
+        <v>1459.6307785935</v>
       </c>
       <c r="G52" t="n">
-        <v>1480.47090404955</v>
+        <v>1473.16740286112</v>
       </c>
     </row>
     <row r="53">
@@ -1622,16 +1622,16 @@
         <v>9</v>
       </c>
       <c r="D53" t="n">
-        <v>1503.13652913778</v>
+        <v>1503.92276911072</v>
       </c>
       <c r="E53" t="s">
         <v>11</v>
       </c>
       <c r="F53" t="n">
-        <v>1488.63684355095</v>
+        <v>1497.50447202654</v>
       </c>
       <c r="G53" t="n">
-        <v>1517.6362147246</v>
+        <v>1510.34106619489</v>
       </c>
     </row>
     <row r="54">
@@ -1645,16 +1645,16 @@
         <v>9</v>
       </c>
       <c r="D54" t="n">
-        <v>1527.95273076133</v>
+        <v>1528.94553680891</v>
       </c>
       <c r="E54" t="s">
         <v>12</v>
       </c>
       <c r="F54" t="n">
-        <v>1513.45304517449</v>
+        <v>1522.9117459548</v>
       </c>
       <c r="G54" t="n">
-        <v>1542.45241634816</v>
+        <v>1534.97932766301</v>
       </c>
     </row>
     <row r="55">
@@ -1668,16 +1668,16 @@
         <v>9</v>
       </c>
       <c r="D55" t="n">
-        <v>1550.43681321925</v>
+        <v>1551.25009246626</v>
       </c>
       <c r="E55" t="s">
         <v>13</v>
       </c>
       <c r="F55" t="n">
-        <v>1535.93712763243</v>
+        <v>1545.91561126845</v>
       </c>
       <c r="G55" t="n">
-        <v>1564.93649880608</v>
+        <v>1556.58457366407</v>
       </c>
     </row>
     <row r="56">
@@ -1691,16 +1691,16 @@
         <v>9</v>
       </c>
       <c r="D56" t="n">
-        <v>1564.9560268038</v>
+        <v>1565.37939874246</v>
       </c>
       <c r="E56" t="s">
         <v>14</v>
       </c>
       <c r="F56" t="n">
-        <v>1550.45634121697</v>
+        <v>1560.81319484242</v>
       </c>
       <c r="G56" t="n">
-        <v>1579.45571239063</v>
+        <v>1569.94560264251</v>
       </c>
     </row>
     <row r="57">
@@ -1714,16 +1714,16 @@
         <v>9</v>
       </c>
       <c r="D57" t="n">
-        <v>1582.43447915199</v>
+        <v>1582.26370113092</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
       </c>
       <c r="F57" t="n">
-        <v>1567.93479356515</v>
+        <v>1577.86290776846</v>
       </c>
       <c r="G57" t="n">
-        <v>1596.93416473882</v>
+        <v>1586.66449449339</v>
       </c>
     </row>
     <row r="58">
@@ -1737,16 +1737,16 @@
         <v>9</v>
       </c>
       <c r="D58" t="n">
-        <v>1602.9520435536</v>
+        <v>1603.43608005313</v>
       </c>
       <c r="E58" t="s">
         <v>16</v>
       </c>
       <c r="F58" t="n">
-        <v>1588.45235796678</v>
+        <v>1597.46951493417</v>
       </c>
       <c r="G58" t="n">
-        <v>1617.45172914042</v>
+        <v>1609.40264517209</v>
       </c>
     </row>
     <row r="59">
@@ -1760,16 +1760,16 @@
         <v>9</v>
       </c>
       <c r="D59" t="n">
-        <v>1622.96910984874</v>
+        <v>1622.9411500891</v>
       </c>
       <c r="E59" t="s">
         <v>17</v>
       </c>
       <c r="F59" t="n">
-        <v>1608.46942426191</v>
+        <v>1617.14558221778</v>
       </c>
       <c r="G59" t="n">
-        <v>1637.46879543557</v>
+        <v>1628.73671796042</v>
       </c>
     </row>
     <row r="60">
@@ -1783,16 +1783,16 @@
         <v>9</v>
       </c>
       <c r="D60" t="n">
-        <v>1625.86721783754</v>
+        <v>1626.98678877549</v>
       </c>
       <c r="E60" t="s">
         <v>18</v>
       </c>
       <c r="F60" t="n">
-        <v>1611.36753225071</v>
+        <v>1617.10867479824</v>
       </c>
       <c r="G60" t="n">
-        <v>1640.36690342437</v>
+        <v>1636.86490275274</v>
       </c>
     </row>
     <row r="61">
@@ -1806,16 +1806,16 @@
         <v>9</v>
       </c>
       <c r="D61" t="n">
-        <v>1650.059345813</v>
+        <v>1650.2617153359</v>
       </c>
       <c r="E61" t="s">
         <v>19</v>
       </c>
       <c r="F61" t="n">
-        <v>1635.55966022617</v>
+        <v>1632.64532280099</v>
       </c>
       <c r="G61" t="n">
-        <v>1664.55903139984</v>
+        <v>1667.87810787081</v>
       </c>
     </row>
     <row r="62">
@@ -1829,16 +1829,16 @@
         <v>9</v>
       </c>
       <c r="D62" t="n">
-        <v>1466.0380358908</v>
+        <v>1466.20897809566</v>
       </c>
       <c r="E62" t="s">
         <v>10</v>
       </c>
       <c r="F62" t="n">
-        <v>1451.53835030397</v>
+        <v>1460.69191157393</v>
       </c>
       <c r="G62" t="n">
-        <v>1480.53772147764</v>
+        <v>1471.7260446174</v>
       </c>
     </row>
     <row r="63">
@@ -1852,16 +1852,16 @@
         <v>9</v>
       </c>
       <c r="D63" t="n">
-        <v>1498.66264461507</v>
+        <v>1499.53229186651</v>
       </c>
       <c r="E63" t="s">
         <v>11</v>
       </c>
       <c r="F63" t="n">
-        <v>1484.16295902825</v>
+        <v>1495.07359496057</v>
       </c>
       <c r="G63" t="n">
-        <v>1513.1623302019</v>
+        <v>1503.99098877246</v>
       </c>
     </row>
     <row r="64">
@@ -1875,16 +1875,16 @@
         <v>9</v>
       </c>
       <c r="D64" t="n">
-        <v>1524.14850891461</v>
+        <v>1525.11817714158</v>
       </c>
       <c r="E64" t="s">
         <v>12</v>
       </c>
       <c r="F64" t="n">
-        <v>1509.64882332778</v>
+        <v>1520.9748494115</v>
       </c>
       <c r="G64" t="n">
-        <v>1538.64819450145</v>
+        <v>1529.26150487167</v>
       </c>
     </row>
     <row r="65">
@@ -1898,16 +1898,16 @@
         <v>9</v>
       </c>
       <c r="D65" t="n">
-        <v>1544.34584882862</v>
+        <v>1544.73387637479</v>
       </c>
       <c r="E65" t="s">
         <v>13</v>
       </c>
       <c r="F65" t="n">
-        <v>1529.84616324179</v>
+        <v>1541.56313357878</v>
       </c>
       <c r="G65" t="n">
-        <v>1558.84553441544</v>
+        <v>1547.90461917079</v>
       </c>
     </row>
     <row r="66">
@@ -1921,16 +1921,16 @@
         <v>9</v>
       </c>
       <c r="D66" t="n">
-        <v>1561.69331816003</v>
+        <v>1561.23130205924</v>
       </c>
       <c r="E66" t="s">
         <v>14</v>
       </c>
       <c r="F66" t="n">
-        <v>1547.1936325732</v>
+        <v>1559.17309329367</v>
       </c>
       <c r="G66" t="n">
-        <v>1576.19300374685</v>
+        <v>1563.28951082481</v>
       </c>
     </row>
     <row r="67">
@@ -1944,16 +1944,16 @@
         <v>9</v>
       </c>
       <c r="D67" t="n">
-        <v>1577.33711201362</v>
+        <v>1576.31729031337</v>
       </c>
       <c r="E67" t="s">
         <v>15</v>
       </c>
       <c r="F67" t="n">
-        <v>1562.83742642679</v>
+        <v>1572.34577156272</v>
       </c>
       <c r="G67" t="n">
-        <v>1591.83679760045</v>
+        <v>1580.28880906402</v>
       </c>
     </row>
     <row r="68">
@@ -1967,16 +1967,16 @@
         <v>9</v>
       </c>
       <c r="D68" t="n">
-        <v>1591.8860800745</v>
+        <v>1590.20735045298</v>
       </c>
       <c r="E68" t="s">
         <v>16</v>
       </c>
       <c r="F68" t="n">
-        <v>1577.38639448768</v>
+        <v>1585.82975779444</v>
       </c>
       <c r="G68" t="n">
-        <v>1606.38576566132</v>
+        <v>1594.58494311151</v>
       </c>
     </row>
     <row r="69">
@@ -1990,16 +1990,16 @@
         <v>9</v>
       </c>
       <c r="D69" t="n">
-        <v>1605.144011005</v>
+        <v>1601.9559393197</v>
       </c>
       <c r="E69" t="s">
         <v>17</v>
       </c>
       <c r="F69" t="n">
-        <v>1590.64432541817</v>
+        <v>1593.96839939139</v>
       </c>
       <c r="G69" t="n">
-        <v>1619.64369659183</v>
+        <v>1609.943479248</v>
       </c>
     </row>
     <row r="70">
@@ -2013,16 +2013,16 @@
         <v>9</v>
       </c>
       <c r="D70" t="n">
-        <v>1622.76903544659</v>
+        <v>1618.92643105831</v>
       </c>
       <c r="E70" t="s">
         <v>18</v>
       </c>
       <c r="F70" t="n">
-        <v>1608.26934985976</v>
+        <v>1606.54210579783</v>
       </c>
       <c r="G70" t="n">
-        <v>1637.26872103342</v>
+        <v>1631.31075631879</v>
       </c>
     </row>
     <row r="71">
@@ -2036,16 +2036,16 @@
         <v>9</v>
       </c>
       <c r="D71" t="n">
-        <v>1627.27217295832</v>
+        <v>1620.81334305439</v>
       </c>
       <c r="E71" t="s">
         <v>19</v>
       </c>
       <c r="F71" t="n">
-        <v>1612.77248737148</v>
+        <v>1606.2902761073</v>
       </c>
       <c r="G71" t="n">
-        <v>1641.77185854515</v>
+        <v>1635.33641000148</v>
       </c>
     </row>
     <row r="72">
@@ -2059,16 +2059,16 @@
         <v>9</v>
       </c>
       <c r="D72" t="n">
-        <v>1460.64878932394</v>
+        <v>1461.07080588867</v>
       </c>
       <c r="E72" t="s">
         <v>10</v>
       </c>
       <c r="F72" t="n">
-        <v>1445.17283248869</v>
+        <v>1458.01971503663</v>
       </c>
       <c r="G72" t="n">
-        <v>1476.12474615919</v>
+        <v>1464.1218967407</v>
       </c>
     </row>
     <row r="73">
@@ -2082,16 +2082,16 @@
         <v>9</v>
       </c>
       <c r="D73" t="n">
-        <v>1493.25976832439</v>
+        <v>1493.33723535333</v>
       </c>
       <c r="E73" t="s">
         <v>11</v>
       </c>
       <c r="F73" t="n">
-        <v>1477.78381148915</v>
+        <v>1491.07424866912</v>
       </c>
       <c r="G73" t="n">
-        <v>1508.73572515964</v>
+        <v>1495.60022203755</v>
       </c>
     </row>
     <row r="74">
@@ -2105,16 +2105,16 @@
         <v>9</v>
       </c>
       <c r="D74" t="n">
-        <v>1520.8493938717</v>
+        <v>1520.48299288863</v>
       </c>
       <c r="E74" t="s">
         <v>12</v>
       </c>
       <c r="F74" t="n">
-        <v>1505.37343703645</v>
+        <v>1518.98708601878</v>
       </c>
       <c r="G74" t="n">
-        <v>1536.32535070695</v>
+        <v>1521.97889975848</v>
       </c>
     </row>
     <row r="75">
@@ -2128,16 +2128,16 @@
         <v>9</v>
       </c>
       <c r="D75" t="n">
-        <v>1542.14608583191</v>
+        <v>1542.27243191754</v>
       </c>
       <c r="E75" t="s">
         <v>13</v>
       </c>
       <c r="F75" t="n">
-        <v>1526.67012899667</v>
+        <v>1541.37524590678</v>
       </c>
       <c r="G75" t="n">
-        <v>1557.62204266716</v>
+        <v>1543.16961792829</v>
       </c>
     </row>
     <row r="76">
@@ -2151,16 +2151,16 @@
         <v>9</v>
       </c>
       <c r="D76" t="n">
-        <v>1556.88468409553</v>
+        <v>1557.49668229535</v>
       </c>
       <c r="E76" t="s">
         <v>14</v>
       </c>
       <c r="F76" t="n">
-        <v>1541.40872726029</v>
+        <v>1555.91607969198</v>
       </c>
       <c r="G76" t="n">
-        <v>1572.36064093078</v>
+        <v>1559.07728489872</v>
       </c>
     </row>
     <row r="77">
@@ -2174,16 +2174,16 @@
         <v>9</v>
       </c>
       <c r="D77" t="n">
-        <v>1573.94774611051</v>
+        <v>1575.05765921474</v>
       </c>
       <c r="E77" t="s">
         <v>15</v>
       </c>
       <c r="F77" t="n">
-        <v>1558.47178927526</v>
+        <v>1572.16752750161</v>
       </c>
       <c r="G77" t="n">
-        <v>1589.42370294576</v>
+        <v>1577.94779092787</v>
       </c>
     </row>
     <row r="78">
@@ -2197,16 +2197,16 @@
         <v>9</v>
       </c>
       <c r="D78" t="n">
-        <v>1589.83142825459</v>
+        <v>1591.75188144512</v>
       </c>
       <c r="E78" t="s">
         <v>16</v>
       </c>
       <c r="F78" t="n">
-        <v>1574.35547141935</v>
+        <v>1586.88589854176</v>
       </c>
       <c r="G78" t="n">
-        <v>1605.30738508983</v>
+        <v>1596.61786434849</v>
       </c>
     </row>
     <row r="79">
@@ -2220,16 +2220,16 @@
         <v>9</v>
       </c>
       <c r="D79" t="n">
-        <v>1596.6355749235</v>
+        <v>1600.22551422072</v>
       </c>
       <c r="E79" t="s">
         <v>17</v>
       </c>
       <c r="F79" t="n">
-        <v>1581.15961808825</v>
+        <v>1592.89207802074</v>
       </c>
       <c r="G79" t="n">
-        <v>1612.11153175874</v>
+        <v>1607.55895042071</v>
       </c>
     </row>
     <row r="80">
@@ -2243,16 +2243,16 @@
         <v>9</v>
       </c>
       <c r="D80" t="n">
-        <v>1600.70551579115</v>
+        <v>1605.44704307456</v>
       </c>
       <c r="E80" t="s">
         <v>18</v>
       </c>
       <c r="F80" t="n">
-        <v>1585.2295589559</v>
+        <v>1595.0665579474</v>
       </c>
       <c r="G80" t="n">
-        <v>1616.1814726264</v>
+        <v>1615.82752820171</v>
       </c>
     </row>
     <row r="81">
@@ -2266,16 +2266,16 @@
         <v>9</v>
       </c>
       <c r="D81" t="n">
-        <v>1608.57982228409</v>
+        <v>1615.0285397341</v>
       </c>
       <c r="E81" t="s">
         <v>19</v>
       </c>
       <c r="F81" t="n">
-        <v>1593.10386544884</v>
+        <v>1599.87239167766</v>
       </c>
       <c r="G81" t="n">
-        <v>1624.05577911934</v>
+        <v>1630.18468779054</v>
       </c>
     </row>
     <row r="82">
@@ -2289,16 +2289,16 @@
         <v>9</v>
       </c>
       <c r="D82" t="n">
-        <v>1334.25125850156</v>
+        <v>1334.7759967317</v>
       </c>
       <c r="E82" t="s">
         <v>10</v>
       </c>
       <c r="F82" t="n">
-        <v>1306.76032520736</v>
+        <v>1325.69347980301</v>
       </c>
       <c r="G82" t="n">
-        <v>1361.74219179577</v>
+        <v>1343.8585136604</v>
       </c>
     </row>
     <row r="83">
@@ -2312,16 +2312,16 @@
         <v>9</v>
       </c>
       <c r="D83" t="n">
-        <v>1360.39308848437</v>
+        <v>1360.87114491191</v>
       </c>
       <c r="E83" t="s">
         <v>11</v>
       </c>
       <c r="F83" t="n">
-        <v>1332.90215519009</v>
+        <v>1350.11272632006</v>
       </c>
       <c r="G83" t="n">
-        <v>1387.88402177866</v>
+        <v>1371.62956350375</v>
       </c>
     </row>
     <row r="84">
@@ -2335,16 +2335,16 @@
         <v>9</v>
       </c>
       <c r="D84" t="n">
-        <v>1379.02333931669</v>
+        <v>1379.07320481593</v>
       </c>
       <c r="E84" t="s">
         <v>12</v>
       </c>
       <c r="F84" t="n">
-        <v>1351.53240602239</v>
+        <v>1366.55150411012</v>
       </c>
       <c r="G84" t="n">
-        <v>1406.514272611</v>
+        <v>1391.59490552173</v>
       </c>
     </row>
     <row r="85">
@@ -2358,16 +2358,16 @@
         <v>9</v>
       </c>
       <c r="D85" t="n">
-        <v>1393.64963692181</v>
+        <v>1393.1251588289</v>
       </c>
       <c r="E85" t="s">
         <v>13</v>
       </c>
       <c r="F85" t="n">
-        <v>1366.15870362748</v>
+        <v>1379.58538189996</v>
       </c>
       <c r="G85" t="n">
-        <v>1421.14057021614</v>
+        <v>1406.66493575783</v>
       </c>
     </row>
     <row r="86">
@@ -2381,16 +2381,16 @@
         <v>9</v>
       </c>
       <c r="D86" t="n">
-        <v>1395.94375422358</v>
+        <v>1394.23680991231</v>
       </c>
       <c r="E86" t="s">
         <v>14</v>
       </c>
       <c r="F86" t="n">
-        <v>1368.45282092927</v>
+        <v>1381.74493982222</v>
       </c>
       <c r="G86" t="n">
-        <v>1423.4346875179</v>
+        <v>1406.72868000241</v>
       </c>
     </row>
     <row r="87">
@@ -2404,16 +2404,16 @@
         <v>9</v>
       </c>
       <c r="D87" t="n">
-        <v>1394.67500741167</v>
+        <v>1394.34288434145</v>
       </c>
       <c r="E87" t="s">
         <v>15</v>
       </c>
       <c r="F87" t="n">
-        <v>1367.18407411734</v>
+        <v>1381.14082853632</v>
       </c>
       <c r="G87" t="n">
-        <v>1422.16594070599</v>
+        <v>1407.54494014659</v>
       </c>
     </row>
     <row r="88">
@@ -2427,16 +2427,16 @@
         <v>9</v>
       </c>
       <c r="D88" t="n">
-        <v>1409.4325894451</v>
+        <v>1409.65234730498</v>
       </c>
       <c r="E88" t="s">
         <v>16</v>
       </c>
       <c r="F88" t="n">
-        <v>1381.94165615076</v>
+        <v>1392.34980785024</v>
       </c>
       <c r="G88" t="n">
-        <v>1436.92352273943</v>
+        <v>1426.95488675971</v>
       </c>
     </row>
     <row r="89">
@@ -2450,16 +2450,16 @@
         <v>9</v>
       </c>
       <c r="D89" t="n">
-        <v>1419.89032780191</v>
+        <v>1421.16211499983</v>
       </c>
       <c r="E89" t="s">
         <v>17</v>
       </c>
       <c r="F89" t="n">
-        <v>1392.39939450758</v>
+        <v>1400.32985270196</v>
       </c>
       <c r="G89" t="n">
-        <v>1447.38126109625</v>
+        <v>1441.9943772977</v>
       </c>
     </row>
     <row r="90">
@@ -2473,16 +2473,16 @@
         <v>9</v>
       </c>
       <c r="D90" t="n">
-        <v>1429.50915350633</v>
+        <v>1432.16958338379</v>
       </c>
       <c r="E90" t="s">
         <v>18</v>
       </c>
       <c r="F90" t="n">
-        <v>1402.01822021195</v>
+        <v>1407.6704549968</v>
       </c>
       <c r="G90" t="n">
-        <v>1457.00008680071</v>
+        <v>1456.66871177078</v>
       </c>
     </row>
     <row r="91">
@@ -2496,16 +2496,16 @@
         <v>9</v>
       </c>
       <c r="D91" t="n">
-        <v>1445.04097020122</v>
+        <v>1449.83658452758</v>
       </c>
       <c r="E91" t="s">
         <v>19</v>
       </c>
       <c r="F91" t="n">
-        <v>1417.55003690678</v>
+        <v>1416.41648966484</v>
       </c>
       <c r="G91" t="n">
-        <v>1472.53190349565</v>
+        <v>1483.25667939032</v>
       </c>
     </row>
     <row r="92">
@@ -2519,16 +2519,16 @@
         <v>9</v>
       </c>
       <c r="D92" t="n">
-        <v>1320.29069233955</v>
+        <v>1319.39492183437</v>
       </c>
       <c r="E92" t="s">
         <v>10</v>
       </c>
       <c r="F92" t="n">
-        <v>1292.79975904531</v>
+        <v>1314.45648811542</v>
       </c>
       <c r="G92" t="n">
-        <v>1347.7816256338</v>
+        <v>1324.33335555332</v>
       </c>
     </row>
     <row r="93">
@@ -2542,16 +2542,16 @@
         <v>9</v>
       </c>
       <c r="D93" t="n">
-        <v>1370.13829596627</v>
+        <v>1367.3672900857</v>
       </c>
       <c r="E93" t="s">
         <v>11</v>
       </c>
       <c r="F93" t="n">
-        <v>1342.64736267204</v>
+        <v>1363.51930790845</v>
       </c>
       <c r="G93" t="n">
-        <v>1397.6292292605</v>
+        <v>1371.21527226296</v>
       </c>
     </row>
     <row r="94">
@@ -2565,16 +2565,16 @@
         <v>9</v>
       </c>
       <c r="D94" t="n">
-        <v>1388.11703172511</v>
+        <v>1386.49018693555</v>
       </c>
       <c r="E94" t="s">
         <v>12</v>
       </c>
       <c r="F94" t="n">
-        <v>1360.62609843091</v>
+        <v>1383.83473980011</v>
       </c>
       <c r="G94" t="n">
-        <v>1415.60796501932</v>
+        <v>1389.14563407098</v>
       </c>
     </row>
     <row r="95">
@@ -2588,16 +2588,16 @@
         <v>9</v>
       </c>
       <c r="D95" t="n">
-        <v>1395.75064131667</v>
+        <v>1396.03262181442</v>
       </c>
       <c r="E95" t="s">
         <v>13</v>
       </c>
       <c r="F95" t="n">
-        <v>1368.25970802244</v>
+        <v>1393.53151942199</v>
       </c>
       <c r="G95" t="n">
-        <v>1423.24157461089</v>
+        <v>1398.53372420685</v>
       </c>
     </row>
     <row r="96">
@@ -2611,16 +2611,16 @@
         <v>9</v>
       </c>
       <c r="D96" t="n">
-        <v>1411.12700570679</v>
+        <v>1411.0554322232</v>
       </c>
       <c r="E96" t="s">
         <v>14</v>
       </c>
       <c r="F96" t="n">
-        <v>1383.63607241256</v>
+        <v>1407.54284826939</v>
       </c>
       <c r="G96" t="n">
-        <v>1438.61793900102</v>
+        <v>1414.56801617702</v>
       </c>
     </row>
     <row r="97">
@@ -2634,16 +2634,16 @@
         <v>9</v>
       </c>
       <c r="D97" t="n">
-        <v>1414.07429366907</v>
+        <v>1421.78689686842</v>
       </c>
       <c r="E97" t="s">
         <v>15</v>
       </c>
       <c r="F97" t="n">
-        <v>1386.58336037487</v>
+        <v>1416.0785779306</v>
       </c>
       <c r="G97" t="n">
-        <v>1441.56522696327</v>
+        <v>1427.49521580624</v>
       </c>
     </row>
     <row r="98">
@@ -2657,16 +2657,16 @@
         <v>9</v>
       </c>
       <c r="D98" t="n">
-        <v>1427.54193643472</v>
+        <v>1432.61076948178</v>
       </c>
       <c r="E98" t="s">
         <v>16</v>
       </c>
       <c r="F98" t="n">
-        <v>1400.05100314053</v>
+        <v>1427.6750697586</v>
       </c>
       <c r="G98" t="n">
-        <v>1455.03286972892</v>
+        <v>1437.54646920495</v>
       </c>
     </row>
     <row r="99">
@@ -2680,16 +2680,16 @@
         <v>9</v>
       </c>
       <c r="D99" t="n">
-        <v>1435.82284704513</v>
+        <v>1444.57334897987</v>
       </c>
       <c r="E99" t="s">
         <v>17</v>
       </c>
       <c r="F99" t="n">
-        <v>1408.33191375092</v>
+        <v>1437.61264723468</v>
       </c>
       <c r="G99" t="n">
-        <v>1463.31378033934</v>
+        <v>1451.53405072506</v>
       </c>
     </row>
     <row r="100">
@@ -2703,16 +2703,16 @@
         <v>9</v>
       </c>
       <c r="D100" t="n">
-        <v>1442.69914762389</v>
+        <v>1450.8686658003</v>
       </c>
       <c r="E100" t="s">
         <v>18</v>
       </c>
       <c r="F100" t="n">
-        <v>1415.20821432968</v>
+        <v>1441.29652859324</v>
       </c>
       <c r="G100" t="n">
-        <v>1470.19008091811</v>
+        <v>1460.44080300736</v>
       </c>
     </row>
     <row r="101">
@@ -2726,16 +2726,16 @@
         <v>9</v>
       </c>
       <c r="D101" t="n">
-        <v>1444.81639262382</v>
+        <v>1455.04260530625</v>
       </c>
       <c r="E101" t="s">
         <v>19</v>
       </c>
       <c r="F101" t="n">
-        <v>1417.32545932961</v>
+        <v>1445.29895321311</v>
       </c>
       <c r="G101" t="n">
-        <v>1472.30732591802</v>
+        <v>1464.78625739939</v>
       </c>
     </row>
     <row r="102">
@@ -2749,16 +2749,16 @@
         <v>9</v>
       </c>
       <c r="D102" t="n">
-        <v>1319.92546275497</v>
+        <v>1317.36914839553</v>
       </c>
       <c r="E102" t="s">
         <v>10</v>
       </c>
       <c r="F102" t="n">
-        <v>1292.43452946072</v>
+        <v>1313.6219396398</v>
       </c>
       <c r="G102" t="n">
-        <v>1347.41639604921</v>
+        <v>1321.11635715126</v>
       </c>
     </row>
     <row r="103">
@@ -2772,16 +2772,16 @@
         <v>9</v>
       </c>
       <c r="D103" t="n">
-        <v>1363.96499321878</v>
+        <v>1363.10180161774</v>
       </c>
       <c r="E103" t="s">
         <v>11</v>
       </c>
       <c r="F103" t="n">
-        <v>1336.47405992455</v>
+        <v>1359.29041467857</v>
       </c>
       <c r="G103" t="n">
-        <v>1391.45592651301</v>
+        <v>1366.91318855692</v>
       </c>
     </row>
     <row r="104">
@@ -2795,16 +2795,16 @@
         <v>9</v>
       </c>
       <c r="D104" t="n">
-        <v>1392.6620962296</v>
+        <v>1392.95677653619</v>
       </c>
       <c r="E104" t="s">
         <v>12</v>
       </c>
       <c r="F104" t="n">
-        <v>1365.17116293539</v>
+        <v>1388.54901586426</v>
       </c>
       <c r="G104" t="n">
-        <v>1420.1530295238</v>
+        <v>1397.36453720812</v>
       </c>
     </row>
     <row r="105">
@@ -2818,16 +2818,16 @@
         <v>9</v>
       </c>
       <c r="D105" t="n">
-        <v>1406.56846035581</v>
+        <v>1407.10217524506</v>
       </c>
       <c r="E105" t="s">
         <v>13</v>
       </c>
       <c r="F105" t="n">
-        <v>1379.07752706159</v>
+        <v>1401.34055150919</v>
       </c>
       <c r="G105" t="n">
-        <v>1434.05939365004</v>
+        <v>1412.86379898094</v>
       </c>
     </row>
     <row r="106">
@@ -2841,16 +2841,16 @@
         <v>9</v>
       </c>
       <c r="D106" t="n">
-        <v>1418.09497874457</v>
+        <v>1418.91440528813</v>
       </c>
       <c r="E106" t="s">
         <v>14</v>
       </c>
       <c r="F106" t="n">
-        <v>1390.60404545034</v>
+        <v>1411.43283878854</v>
       </c>
       <c r="G106" t="n">
-        <v>1445.5859120388</v>
+        <v>1426.39597178772</v>
       </c>
     </row>
     <row r="107">
@@ -2864,16 +2864,16 @@
         <v>9</v>
       </c>
       <c r="D107" t="n">
-        <v>1437.08695301754</v>
+        <v>1438.2785552549</v>
       </c>
       <c r="E107" t="s">
         <v>15</v>
       </c>
       <c r="F107" t="n">
-        <v>1409.59601972334</v>
+        <v>1430.96995854993</v>
       </c>
       <c r="G107" t="n">
-        <v>1464.57788631174</v>
+        <v>1445.58715195987</v>
       </c>
     </row>
     <row r="108">
@@ -2887,16 +2887,16 @@
         <v>9</v>
       </c>
       <c r="D108" t="n">
-        <v>1446.12859064387</v>
+        <v>1448.75322288979</v>
       </c>
       <c r="E108" t="s">
         <v>16</v>
       </c>
       <c r="F108" t="n">
-        <v>1418.63765734968</v>
+        <v>1438.11204659539</v>
       </c>
       <c r="G108" t="n">
-        <v>1473.61952393807</v>
+        <v>1459.39439918419</v>
       </c>
     </row>
     <row r="109">
@@ -2910,16 +2910,16 @@
         <v>9</v>
       </c>
       <c r="D109" t="n">
-        <v>1445.8792095678</v>
+        <v>1446.08278845038</v>
       </c>
       <c r="E109" t="s">
         <v>17</v>
       </c>
       <c r="F109" t="n">
-        <v>1418.38827627359</v>
+        <v>1434.93060826586</v>
       </c>
       <c r="G109" t="n">
-        <v>1473.37014286201</v>
+        <v>1457.23496863489</v>
       </c>
     </row>
     <row r="110">
@@ -2933,16 +2933,16 @@
         <v>9</v>
       </c>
       <c r="D110" t="n">
-        <v>1455.28732358106</v>
+        <v>1460.49454632805</v>
       </c>
       <c r="E110" t="s">
         <v>18</v>
       </c>
       <c r="F110" t="n">
-        <v>1427.79639028685</v>
+        <v>1449.00858786096</v>
       </c>
       <c r="G110" t="n">
-        <v>1482.77825687527</v>
+        <v>1471.98050479515</v>
       </c>
     </row>
     <row r="111">
@@ -2956,16 +2956,16 @@
         <v>9</v>
       </c>
       <c r="D111" t="n">
-        <v>1476.39933667719</v>
+        <v>1482.85281223378</v>
       </c>
       <c r="E111" t="s">
         <v>19</v>
       </c>
       <c r="F111" t="n">
-        <v>1448.90840338298</v>
+        <v>1465.39216439286</v>
       </c>
       <c r="G111" t="n">
-        <v>1503.89026997139</v>
+        <v>1500.31346007469</v>
       </c>
     </row>
     <row r="112">
@@ -2979,16 +2979,16 @@
         <v>9</v>
       </c>
       <c r="D112" t="n">
-        <v>1319.56681752318</v>
+        <v>1313.37658323827</v>
       </c>
       <c r="E112" t="s">
         <v>10</v>
       </c>
       <c r="F112" t="n">
-        <v>1291.09340939808</v>
+        <v>1310.6184820365</v>
       </c>
       <c r="G112" t="n">
-        <v>1348.04022564828</v>
+        <v>1316.13468444004</v>
       </c>
     </row>
     <row r="113">
@@ -3002,16 +3002,16 @@
         <v>9</v>
       </c>
       <c r="D113" t="n">
-        <v>1353.53237782684</v>
+        <v>1348.89516421169</v>
       </c>
       <c r="E113" t="s">
         <v>11</v>
       </c>
       <c r="F113" t="n">
-        <v>1325.05896970176</v>
+        <v>1347.26041986182</v>
       </c>
       <c r="G113" t="n">
-        <v>1382.00578595193</v>
+        <v>1350.52990856157</v>
       </c>
     </row>
     <row r="114">
@@ -3025,16 +3025,16 @@
         <v>9</v>
       </c>
       <c r="D114" t="n">
-        <v>1386.60606058981</v>
+        <v>1383.04854096681</v>
       </c>
       <c r="E114" t="s">
         <v>12</v>
       </c>
       <c r="F114" t="n">
-        <v>1358.13265246475</v>
+        <v>1381.34358670081</v>
       </c>
       <c r="G114" t="n">
-        <v>1415.07946871487</v>
+        <v>1384.75349523281</v>
       </c>
     </row>
     <row r="115">
@@ -3048,16 +3048,16 @@
         <v>9</v>
       </c>
       <c r="D115" t="n">
-        <v>1402.46180883578</v>
+        <v>1402.08529059365</v>
       </c>
       <c r="E115" t="s">
         <v>13</v>
       </c>
       <c r="F115" t="n">
-        <v>1373.9884007107</v>
+        <v>1398.16393329229</v>
       </c>
       <c r="G115" t="n">
-        <v>1430.93521696086</v>
+        <v>1406.006647895</v>
       </c>
     </row>
     <row r="116">
@@ -3071,16 +3071,16 @@
         <v>9</v>
       </c>
       <c r="D116" t="n">
-        <v>1415.13515240547</v>
+        <v>1415.74831163945</v>
       </c>
       <c r="E116" t="s">
         <v>14</v>
       </c>
       <c r="F116" t="n">
-        <v>1386.66174428038</v>
+        <v>1410.94397023954</v>
       </c>
       <c r="G116" t="n">
-        <v>1443.60856053055</v>
+        <v>1420.55265303936</v>
       </c>
     </row>
     <row r="117">
@@ -3094,16 +3094,16 @@
         <v>9</v>
       </c>
       <c r="D117" t="n">
-        <v>1430.77294781239</v>
+        <v>1433.37743386755</v>
       </c>
       <c r="E117" t="s">
         <v>15</v>
       </c>
       <c r="F117" t="n">
-        <v>1402.29953968732</v>
+        <v>1426.61554136647</v>
       </c>
       <c r="G117" t="n">
-        <v>1459.24635593745</v>
+        <v>1440.13932636863</v>
       </c>
     </row>
     <row r="118">
@@ -3117,16 +3117,16 @@
         <v>9</v>
       </c>
       <c r="D118" t="n">
-        <v>1434.68041283376</v>
+        <v>1434.78329701505</v>
       </c>
       <c r="E118" t="s">
         <v>16</v>
       </c>
       <c r="F118" t="n">
-        <v>1406.2070047087</v>
+        <v>1429.43547334676</v>
       </c>
       <c r="G118" t="n">
-        <v>1463.15382095881</v>
+        <v>1440.13112068335</v>
       </c>
     </row>
     <row r="119">
@@ -3140,16 +3140,16 @@
         <v>9</v>
       </c>
       <c r="D119" t="n">
-        <v>1442.20432385528</v>
+        <v>1442.59818799787</v>
       </c>
       <c r="E119" t="s">
         <v>17</v>
       </c>
       <c r="F119" t="n">
-        <v>1413.73091573021</v>
+        <v>1436.20992789429</v>
       </c>
       <c r="G119" t="n">
-        <v>1470.67773198035</v>
+        <v>1448.98644810146</v>
       </c>
     </row>
     <row r="120">
@@ -3163,16 +3163,16 @@
         <v>9</v>
       </c>
       <c r="D120" t="n">
-        <v>1434.14828636637</v>
+        <v>1433.15604096388</v>
       </c>
       <c r="E120" t="s">
         <v>18</v>
       </c>
       <c r="F120" t="n">
-        <v>1405.6748782413</v>
+        <v>1426.12592074992</v>
       </c>
       <c r="G120" t="n">
-        <v>1462.62169449143</v>
+        <v>1440.18616117783</v>
       </c>
     </row>
     <row r="121">
@@ -3186,16 +3186,16 @@
         <v>9</v>
       </c>
       <c r="D121" t="n">
-        <v>1453.10577321334</v>
+        <v>1455.10202003855</v>
       </c>
       <c r="E121" t="s">
         <v>19</v>
       </c>
       <c r="F121" t="n">
-        <v>1424.63236508828</v>
+        <v>1446.75168404094</v>
       </c>
       <c r="G121" t="n">
-        <v>1481.57918133841</v>
+        <v>1463.45235603615</v>
       </c>
     </row>
   </sheetData>
